--- a/testData/LoginData.xlsx
+++ b/testData/LoginData.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Intellij\SeleniumWorkspace\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58EBB13-6ADC-4316-9ED1-750C742D65F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31177A52-211B-4DA8-8DCB-C38C3C67619B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>username</t>
   </si>
@@ -41,18 +41,11 @@
   <si>
     <t>Result</t>
   </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -62,7 +55,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -73,26 +66,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,12 +96,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,37 +384,33 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s" s="3">
-        <v>5</v>
-      </c>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B3" s="1">
         <v>21324</v>
       </c>
-      <c r="C3" t="s" s="4">
-        <v>6</v>
-      </c>
+      <c r="C3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
